--- a/Not_Formulated_Incentive_Traced.xlsx
+++ b/Not_Formulated_Incentive_Traced.xlsx
@@ -603,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2556,88 +2556,170 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>EF12635</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Pallav Sarkar</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Traced — matches submitted exactly</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>YES — Formula Based / Verified / No Risk</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Email 'Fwd: Approval Request for Overtime Payment – Support Agents' — Dibakar Pramanik to Vishal Kumar/Munira Chasmawala, approved by Vishal Kumar ('Approved', 23 Jul 2026), forwarded to Mithun Jaiswar by Munira Chasmawala 8 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>EF12634</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Abhishek Kumar Ram</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>Traced — matches submitted exactly</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>YES — Formula Based / Verified / No Risk</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Email 'Fwd: Approval Request for Overtime Payment – Support Agents' — Dibakar Pramanik to Vishal Kumar/Munira Chasmawala, approved by Vishal Kumar ('Approved', 23 Jul 2026), forwarded to Mithun Jaiswar by Munira Chasmawala 8 Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Traced — matches submitted exactly</t>
         </is>
       </c>
-      <c r="B53" s="13" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="B55" s="13" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>Traced — matches within a few rupees</t>
         </is>
       </c>
-      <c r="B54" s="13" t="n">
+      <c r="B56" s="13" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="14" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Traced — source found, but gap or no formula shown</t>
         </is>
       </c>
-      <c r="B55" s="13" t="n">
+      <c r="B57" s="13" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="14" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
         <is>
           <t>Traced — explains the figure, not a formula</t>
         </is>
       </c>
-      <c r="B56" s="13" t="n">
+      <c r="B58" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Link followed — employee not found at source</t>
         </is>
       </c>
-      <c r="B57" s="13" t="n">
+      <c r="B59" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="13" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Total links traced</t>
         </is>
       </c>
-      <c r="B58" s="13" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="B60" s="13" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
         <is>
           <t>Reclassified to Formula Based / Verified / No Risk</t>
         </is>
       </c>
-      <c r="B59" s="13" t="n">
-        <v>8</v>
+      <c r="B61" s="13" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20320,38 +20402,39 @@
           <t>Online support</t>
         </is>
       </c>
-      <c r="G220" s="16" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="H220" s="16" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I220" s="16" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J220" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G220" s="20" t="inlineStr">
+        <is>
+          <t>Formula Based</t>
+        </is>
+      </c>
+      <c r="H220" s="20" t="inlineStr">
+        <is>
+          <t>Formulated</t>
+        </is>
+      </c>
+      <c r="I220" s="20" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J220" s="20" t="inlineStr">
+        <is>
+          <t>No Risk</t>
         </is>
       </c>
       <c r="K220" s="17" t="n">
         <v>1800</v>
       </c>
       <c r="L220" s="17" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="M220" s="17" t="n">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="N220" s="18" t="inlineStr">
         <is>
-          <t>Submitted payout: 1 × ₹1,800 = ₹1,800. No role-aligned employee-level count × rate/slab calculation was found in the supplied Kolkata internal, Recruitment, Department, FSE Central or FSE calculation files.</t>
+          <t>RECLASSIFIED — reproducible formula found. Source: Email 'Fwd: Approval Request for Overtime Payment – Support Agents' — Dibakar Pramanik to Vishal Kumar/Munira Chasmawala, approved by Vishal Kumar ('Approved', 23 Jul 2026), forwarded to Mithun Jaiswar by Munira Chasmawala 8 Aug 2026
+Finding: OT calculation in the approval email: Pallav Sarkar — Rs300/hr x 3 hours = Rs900/day x 2 days (12-Jul-2026, 18-Jul-2026, both 20:00-08:00 weekend shifts) = Rs1,800. Exact match to submitted amount. Full chain present: request -&gt; named approver 'Approved' -&gt; HR processing -&gt; forwarded to Mithun for reference.</t>
         </is>
       </c>
       <c r="O220" s="18" t="inlineStr">
@@ -20365,9 +20448,20 @@
         </is>
       </c>
       <c r="Q220" s="18" t="inlineStr"/>
-      <c r="R220" s="19" t="inlineStr"/>
-      <c r="S220" s="19" t="inlineStr"/>
-      <c r="T220" s="19" t="inlineStr"/>
+      <c r="R220" s="9" t="inlineStr">
+        <is>
+          <t>Traced — matches submitted exactly</t>
+        </is>
+      </c>
+      <c r="S220" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="T220" s="8" t="inlineStr">
+        <is>
+          <t>Source: Email 'Fwd: Approval Request for Overtime Payment – Support Agents' — Dibakar Pramanik to Vishal Kumar/Munira Chasmawala, approved by Vishal Kumar ('Approved', 23 Jul 2026), forwarded to Mithun Jaiswar by Munira Chasmawala 8 Aug 2026
+Finding: OT calculation in the approval email: Pallav Sarkar — Rs300/hr x 3 hours = Rs900/day x 2 days (12-Jul-2026, 18-Jul-2026, both 20:00-08:00 weekend shifts) = Rs1,800. Exact match to submitted amount. Full chain present: request -&gt; named approver 'Approved' -&gt; HR processing -&gt; forwarded to Mithun for reference.</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="16" t="inlineStr">
@@ -20400,38 +20494,39 @@
           <t>Online support</t>
         </is>
       </c>
-      <c r="G221" s="16" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="H221" s="16" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I221" s="16" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J221" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G221" s="20" t="inlineStr">
+        <is>
+          <t>Formula Based</t>
+        </is>
+      </c>
+      <c r="H221" s="20" t="inlineStr">
+        <is>
+          <t>Formulated</t>
+        </is>
+      </c>
+      <c r="I221" s="20" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J221" s="20" t="inlineStr">
+        <is>
+          <t>No Risk</t>
         </is>
       </c>
       <c r="K221" s="17" t="n">
         <v>1800</v>
       </c>
       <c r="L221" s="17" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="M221" s="17" t="n">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="N221" s="18" t="inlineStr">
         <is>
-          <t>Submitted payout: 1 × ₹1,800 = ₹1,800. No role-aligned employee-level count × rate/slab calculation was found in the supplied Kolkata internal, Recruitment, Department, FSE Central or FSE calculation files.</t>
+          <t>RECLASSIFIED — reproducible formula found. Source: Email 'Fwd: Approval Request for Overtime Payment – Support Agents' — Dibakar Pramanik to Vishal Kumar/Munira Chasmawala, approved by Vishal Kumar ('Approved', 23 Jul 2026), forwarded to Mithun Jaiswar by Munira Chasmawala 8 Aug 2026
+Finding: OT calculation in the approval email: Abhishek Ram — Rs300/hr x 3 hours = Rs900/day x 2 days (11-Jul-2026, 19-Jul-2026, both 20:00-08:00 weekend shifts) = Rs1,800. Exact match to submitted amount. Full chain present: request -&gt; named approver 'Approved' -&gt; HR processing -&gt; forwarded to Mithun for reference.</t>
         </is>
       </c>
       <c r="O221" s="18" t="inlineStr">
@@ -20445,9 +20540,20 @@
         </is>
       </c>
       <c r="Q221" s="18" t="inlineStr"/>
-      <c r="R221" s="19" t="inlineStr"/>
-      <c r="S221" s="19" t="inlineStr"/>
-      <c r="T221" s="19" t="inlineStr"/>
+      <c r="R221" s="9" t="inlineStr">
+        <is>
+          <t>Traced — matches submitted exactly</t>
+        </is>
+      </c>
+      <c r="S221" s="5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="T221" s="8" t="inlineStr">
+        <is>
+          <t>Source: Email 'Fwd: Approval Request for Overtime Payment – Support Agents' — Dibakar Pramanik to Vishal Kumar/Munira Chasmawala, approved by Vishal Kumar ('Approved', 23 Jul 2026), forwarded to Mithun Jaiswar by Munira Chasmawala 8 Aug 2026
+Finding: OT calculation in the approval email: Abhishek Ram — Rs300/hr x 3 hours = Rs900/day x 2 days (11-Jul-2026, 19-Jul-2026, both 20:00-08:00 weekend shifts) = Rs1,800. Exact match to submitted amount. Full chain present: request -&gt; named approver 'Approved' -&gt; HR processing -&gt; forwarded to Mithun for reference.</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="16" t="inlineStr">

--- a/Not_Formulated_Incentive_Traced.xlsx
+++ b/Not_Formulated_Incentive_Traced.xlsx
@@ -17482,22 +17482,22 @@
       </c>
       <c r="G185" s="4" t="inlineStr">
         <is>
-          <t>Subjective / Evidence Missing</t>
+          <t>Formula Based (BI)</t>
         </is>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>Not Formulated</t>
+          <t>Formulated</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>Insufficient Evidence</t>
+          <t>Underpaid — No Risk</t>
         </is>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>No Risk</t>
         </is>
       </c>
       <c r="K185" s="5" t="n">
@@ -17511,12 +17511,12 @@
       </c>
       <c r="N185" s="6" t="inlineStr">
         <is>
-          <t>Performance Marketing / Telecalling — no calculation structure located
-   - Submitted payout: 1 x ₹10,000 = ₹10,000
-Role total = ₹10,000
-Source entitlement total: not established
-Submitted = ₹10,000 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Performance Marketing / Telecalling — BI-computed entitlement
+   - BI entitlement for the period = ₹10,252
+Role total (BI) = ₹10,252
+Source entitlement total: OB incentive file (BI-computed entitlement carried in the audit extract) ₹10,252 = ₹10,252
+Submitted = ₹10,000 | Variance = ₹-252
+Evidence: BI produced an independent entitlement for this employee; the payout is BELOW that entitlement, so there is no overpayment exposure on this row.</t>
         </is>
       </c>
       <c r="O185" s="6" t="inlineStr"/>
@@ -17531,7 +17531,7 @@
       <c r="T185" s="8" t="inlineStr"/>
       <c r="U185" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OB incentive file / BI entitlement</t>
         </is>
       </c>
     </row>
@@ -18318,12 +18318,12 @@
       </c>
       <c r="G194" s="4" t="inlineStr">
         <is>
-          <t>Subjective / Evidence Missing</t>
+          <t>Part Formula + Manual/Fixed Component</t>
         </is>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
-          <t>Not Formulated</t>
+          <t>Part Formulated</t>
         </is>
       </c>
       <c r="I194" s="4" t="inlineStr">
@@ -18340,19 +18340,20 @@
         <v>5000</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M194" s="5" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="N194" s="6" t="inlineStr">
         <is>
-          <t>Vehicle management / Vehicle Reconciliation — no calculation structure located
-   - Submitted payout: 1 x ₹5,000 = ₹5,000
-Role total = ₹5,000
-Source entitlement total: not established
-Submitted = ₹5,000 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Vehicle Management / Vehicle Reconciliation — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹5,000
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total = ₹5,000 = ₹5,000
+Source entitlement total: approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹5,000 = ₹5,000
+Submitted = ₹5,000 | Variance = ₹0
+Evidence: amount corroborated by 1 independent source and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O194" s="6" t="inlineStr"/>
@@ -18366,12 +18367,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R194" s="7" t="n"/>
+      <c r="R194" s="7" t="n">
+        <v>5000</v>
+      </c>
       <c r="S194" s="7" t="n"/>
       <c r="T194" s="8" t="inlineStr"/>
       <c r="U194" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore approval email</t>
         </is>
       </c>
     </row>
@@ -18406,43 +18409,44 @@
           <t>Key management</t>
         </is>
       </c>
-      <c r="G195" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H195" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I195" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J195" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G195" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H195" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I195" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J195" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K195" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M195" s="5" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="N195" s="6" t="inlineStr">
         <is>
-          <t>Vehicle management / Key management — no calculation structure located
-   - Submitted payout: 1 x ₹2,000 = ₹2,000
-Role total = ₹2,000
-Source entitlement total: not established
-Submitted = ₹2,000 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Vehicle Management / Key management — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹2,000
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹2,000 = ₹2,000
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹2,000; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹2,000 = ₹2,000
+Submitted = ₹2,000 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O195" s="6" t="inlineStr"/>
@@ -18456,12 +18460,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R195" s="7" t="n"/>
+      <c r="R195" s="7" t="n">
+        <v>2000</v>
+      </c>
       <c r="S195" s="7" t="n"/>
       <c r="T195" s="8" t="inlineStr"/>
       <c r="U195" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -18496,43 +18502,44 @@
           <t>Car stickers</t>
         </is>
       </c>
-      <c r="G196" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I196" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J196" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G196" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H196" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I196" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J196" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K196" s="5" t="n">
         <v>1500</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M196" s="5" t="n">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="N196" s="6" t="inlineStr">
         <is>
-          <t>Vehicle management / Car stickers — no calculation structure located
-   - Submitted payout: 1 x ₹1,500 = ₹1,500
-Role total = ₹1,500
-Source entitlement total: not established
-Submitted = ₹1,500 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Vehicle Management / Car stickers — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹1,500
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹1,500 = ₹1,500
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹1,500; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹1,500 = ₹1,500
+Submitted = ₹1,500 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O196" s="6" t="inlineStr"/>
@@ -18546,12 +18553,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R196" s="7" t="n"/>
+      <c r="R196" s="7" t="n">
+        <v>1500</v>
+      </c>
       <c r="S196" s="7" t="n"/>
       <c r="T196" s="8" t="inlineStr"/>
       <c r="U196" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -18586,43 +18595,44 @@
           <t>RTA final inspection &amp; takeover</t>
         </is>
       </c>
-      <c r="G197" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H197" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J197" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G197" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H197" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I197" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J197" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K197" s="5" t="n">
         <v>1000</v>
       </c>
       <c r="L197" s="5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M197" s="5" t="n">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="N197" s="6" t="inlineStr">
         <is>
-          <t>Vehicle management / RTA final inspection &amp; takeover — no calculation structure located
-   - Submitted payout: 1 x ₹1,000 = ₹1,000
-Role total = ₹1,000
-Source entitlement total: not established
-Submitted = ₹1,000 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Vehicle Management / RTA final inspection — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹1,000
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹1,000 = ₹1,000
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹1,000; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹1,000 = ₹1,000
+Submitted = ₹1,000 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O197" s="6" t="inlineStr"/>
@@ -18636,12 +18646,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R197" s="7" t="n"/>
+      <c r="R197" s="7" t="n">
+        <v>1000</v>
+      </c>
       <c r="S197" s="7" t="n"/>
       <c r="T197" s="8" t="inlineStr"/>
       <c r="U197" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -18676,43 +18688,44 @@
           <t>Hub/ Vehicle Movement</t>
         </is>
       </c>
-      <c r="G198" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H198" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J198" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G198" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H198" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I198" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J198" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
         <v>670</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>0</v>
+        <v>670</v>
       </c>
       <c r="M198" s="5" t="n">
-        <v>-670</v>
+        <v>0</v>
       </c>
       <c r="N198" s="6" t="inlineStr">
         <is>
-          <t>Vehicle management / Hub/ Vehicle Movement — no calculation structure located
-   - Submitted payout: 1 x ₹670 = ₹670
-Role total = ₹670
-Source entitlement total: not established
-Submitted = ₹670 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Vehicle Management / Hub &amp; Vehicle Movement — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹670
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹670 = ₹670
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹670; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹670 = ₹670
+Submitted = ₹670 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O198" s="6" t="inlineStr"/>
@@ -18726,12 +18739,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R198" s="7" t="n"/>
+      <c r="R198" s="7" t="n">
+        <v>670</v>
+      </c>
       <c r="S198" s="7" t="n"/>
       <c r="T198" s="8" t="inlineStr"/>
       <c r="U198" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -18766,43 +18781,44 @@
           <t>Biker</t>
         </is>
       </c>
-      <c r="G199" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H199" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I199" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J199" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G199" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H199" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I199" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J199" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K199" s="5" t="n">
         <v>3500</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="M199" s="5" t="n">
-        <v>-3500</v>
+        <v>0</v>
       </c>
       <c r="N199" s="6" t="inlineStr">
         <is>
-          <t>R&amp;M - EV / Biker — no calculation structure located
-   - Submitted payout: 1 x ₹3,500 = ₹3,500
-Role total = ₹3,500
-Source entitlement total: not established
-Submitted = ₹3,500 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>R&amp;M - EV / Workshop_Incentive — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹3,500
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹3,500 = ₹3,500
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹3,500; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹3,500 = ₹3,500
+Submitted = ₹3,500 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O199" s="6" t="inlineStr"/>
@@ -18816,12 +18832,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R199" s="7" t="n"/>
+      <c r="R199" s="7" t="n">
+        <v>3500</v>
+      </c>
       <c r="S199" s="7" t="n"/>
       <c r="T199" s="8" t="inlineStr"/>
       <c r="U199" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -18856,43 +18874,44 @@
           <t>Online support</t>
         </is>
       </c>
-      <c r="G200" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H200" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I200" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J200" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G200" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H200" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I200" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J200" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K200" s="5" t="n">
         <v>5000</v>
       </c>
       <c r="L200" s="5" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M200" s="5" t="n">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="N200" s="6" t="inlineStr">
         <is>
-          <t>Support / Online support — no calculation structure located
-   - Submitted payout: 1 x ₹5,000 = ₹5,000
-Role total = ₹5,000
-Source entitlement total: not established
-Submitted = ₹5,000 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Support / Ticketing — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹5,000
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹5,000 = ₹5,000
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹5,000; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹5,000 = ₹5,000
+Submitted = ₹5,000 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O200" s="6" t="inlineStr"/>
@@ -18906,12 +18925,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R200" s="7" t="n"/>
+      <c r="R200" s="7" t="n">
+        <v>5000</v>
+      </c>
       <c r="S200" s="7" t="n"/>
       <c r="T200" s="8" t="inlineStr"/>
       <c r="U200" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -18946,43 +18967,44 @@
           <t>Cash Receover</t>
         </is>
       </c>
-      <c r="G201" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H201" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I201" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J201" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G201" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H201" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I201" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J201" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K201" s="5" t="n">
         <v>3254</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>0</v>
+        <v>3254</v>
       </c>
       <c r="M201" s="5" t="n">
-        <v>-3254</v>
+        <v>0</v>
       </c>
       <c r="N201" s="6" t="inlineStr">
         <is>
-          <t>Recovery / Cash Receover — no calculation structure located
-   - Submitted payout: 1 x ₹3,254 = ₹3,254
-Role total = ₹3,254
-Source entitlement total: not established
-Submitted = ₹3,254 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Recovery / Bad Debt — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹3,254
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹3,254 = ₹3,254
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹3,254; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹3,254 = ₹3,254
+Submitted = ₹3,254 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O201" s="6" t="inlineStr"/>
@@ -18996,12 +19018,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R201" s="7" t="n"/>
+      <c r="R201" s="7" t="n">
+        <v>3254</v>
+      </c>
       <c r="S201" s="7" t="n"/>
       <c r="T201" s="8" t="inlineStr"/>
       <c r="U201" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -19036,43 +19060,44 @@
           <t>Telecalling</t>
         </is>
       </c>
-      <c r="G202" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H202" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I202" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J202" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G202" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H202" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I202" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J202" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K202" s="5" t="n">
         <v>2100</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>-2100</v>
+        <v>0</v>
       </c>
       <c r="N202" s="6" t="inlineStr">
         <is>
-          <t>Cash Collections and Performance / Telecalling — no calculation structure located
-   - Submitted payout: 1 x ₹2,100 = ₹2,100
-Role total = ₹2,100
-Source entitlement total: not established
-Submitted = ₹2,100 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Collection / Performance — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹2,100
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹2,100 = ₹2,100
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹2,100; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹2,100 = ₹2,100
+Submitted = ₹2,100 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O202" s="6" t="inlineStr"/>
@@ -19086,12 +19111,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R202" s="7" t="n"/>
+      <c r="R202" s="7" t="n">
+        <v>2100</v>
+      </c>
       <c r="S202" s="7" t="n"/>
       <c r="T202" s="8" t="inlineStr"/>
       <c r="U202" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -19126,43 +19153,44 @@
           <t>Telecalling</t>
         </is>
       </c>
-      <c r="G203" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H203" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I203" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J203" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G203" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H203" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I203" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J203" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K203" s="5" t="n">
         <v>2850</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>0</v>
+        <v>2850</v>
       </c>
       <c r="M203" s="5" t="n">
-        <v>-2850</v>
+        <v>0</v>
       </c>
       <c r="N203" s="6" t="inlineStr">
         <is>
-          <t>Cash Collections and Performance / Telecalling — no calculation structure located
-   - Submitted payout: 1 x ₹2,850 = ₹2,850
-Role total = ₹2,850
-Source entitlement total: not established
-Submitted = ₹2,850 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Collection / Performance — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹2,850
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹2,850 = ₹2,850
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹2,850; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹2,850 = ₹2,850
+Submitted = ₹2,850 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O203" s="6" t="inlineStr"/>
@@ -19176,12 +19204,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R203" s="7" t="n"/>
+      <c r="R203" s="7" t="n">
+        <v>2850</v>
+      </c>
       <c r="S203" s="7" t="n"/>
       <c r="T203" s="8" t="inlineStr"/>
       <c r="U203" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -19216,43 +19246,44 @@
           <t>Operations</t>
         </is>
       </c>
-      <c r="G204" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H204" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I204" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J204" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G204" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H204" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I204" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J204" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K204" s="5" t="n">
         <v>7916</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>0</v>
+        <v>7916</v>
       </c>
       <c r="M204" s="5" t="n">
-        <v>-7916</v>
+        <v>0</v>
       </c>
       <c r="N204" s="6" t="inlineStr">
         <is>
-          <t>Own Now / Operations — no calculation structure located
-   - Submitted payout: 1 x ₹7,916 = ₹7,916
-Role total = ₹7,916
-Source entitlement total: not established
-Submitted = ₹7,916 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Helpdesk / Retention team — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹7,916
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹7,916 = ₹7,916
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹7,916; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹7,916 = ₹7,916
+Submitted = ₹7,916 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O204" s="6" t="inlineStr"/>
@@ -19266,12 +19297,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R204" s="7" t="n"/>
+      <c r="R204" s="7" t="n">
+        <v>7916</v>
+      </c>
       <c r="S204" s="7" t="n"/>
       <c r="T204" s="8" t="inlineStr"/>
       <c r="U204" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -19306,43 +19339,45 @@
           <t>Inhub Support &amp; retention</t>
         </is>
       </c>
-      <c r="G205" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H205" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I205" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J205" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G205" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H205" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I205" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J205" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
         <v>1550</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>0</v>
+        <v>1550</v>
       </c>
       <c r="M205" s="5" t="n">
-        <v>-1550</v>
+        <v>0</v>
       </c>
       <c r="N205" s="6" t="inlineStr">
         <is>
-          <t>Support / Inhub Support &amp; retention — no calculation structure located
-   - Submitted payout: 1 x ₹1,550 = ₹1,550
-Role total = ₹1,550
-Source entitlement total: not established
-Submitted = ₹1,550 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Helpdesk / Retention team — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹1,250
+   - Referral component: ₹300
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹1,250 + ₹300 = ₹1,550
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹1,550; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹1,550 = ₹1,550
+Submitted = ₹1,550 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O205" s="6" t="inlineStr"/>
@@ -19356,12 +19391,20 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R205" s="7" t="n"/>
-      <c r="S205" s="7" t="n"/>
-      <c r="T205" s="8" t="inlineStr"/>
+      <c r="R205" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="S205" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="T205" s="8" t="inlineStr">
+        <is>
+          <t>Referral</t>
+        </is>
+      </c>
       <c r="U205" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -19396,43 +19439,44 @@
           <t>In Hub Onboading</t>
         </is>
       </c>
-      <c r="G206" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H206" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I206" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J206" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G206" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H206" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I206" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J206" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K206" s="5" t="n">
         <v>6250</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>0</v>
+        <v>6250</v>
       </c>
       <c r="M206" s="5" t="n">
-        <v>-6250</v>
+        <v>0</v>
       </c>
       <c r="N206" s="6" t="inlineStr">
         <is>
-          <t>Onboarding / In Hub Onboading — no calculation structure located
-   - Submitted payout: 1 x ₹6,250 = ₹6,250
-Role total = ₹6,250
-Source entitlement total: not established
-Submitted = ₹6,250 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Helpdesk / Retention team — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹6,250
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹6,250 = ₹6,250
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹6,250; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹6,250 = ₹6,250
+Submitted = ₹6,250 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O206" s="6" t="inlineStr"/>
@@ -19446,12 +19490,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R206" s="7" t="n"/>
+      <c r="R206" s="7" t="n">
+        <v>6250</v>
+      </c>
       <c r="S206" s="7" t="n"/>
       <c r="T206" s="8" t="inlineStr"/>
       <c r="U206" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -19486,43 +19532,44 @@
           <t>In Hub Onboading</t>
         </is>
       </c>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H207" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I207" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J207" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G207" s="11" t="inlineStr">
+        <is>
+          <t>Part Formula + Approved Flat Component</t>
+        </is>
+      </c>
+      <c r="H207" s="11" t="inlineStr">
+        <is>
+          <t>Part Formulated</t>
+        </is>
+      </c>
+      <c r="I207" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J207" s="11" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="K207" s="5" t="n">
         <v>4000</v>
       </c>
       <c r="L207" s="5" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="M207" s="5" t="n">
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="N207" s="6" t="inlineStr">
         <is>
-          <t>Onboarding / In Hub Onboading — no calculation structure located
-   - Submitted payout: 1 x ₹4,000 = ₹4,000
-Role total = ₹4,000
-Source entitlement total: not established
-Submitted = ₹4,000 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Onboarding / DTO — city payout file component structure (Amount + Referral + Own Now + DTO)
+   - Base incentive component: ₹4,000
+   - Own Now component: ₹0;  DTO component: ₹0
+Role total (Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab, 'Total' column) = ₹4,000 = ₹4,000
+Source entitlement total: Bangalore Incentive File (MOM) &gt; 'Jul - 2026' tab ₹4,000; approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹4,000 = ₹4,000
+Submitted = ₹4,000 | Variance = ₹0
+Evidence: amount corroborated by 2 independent sources and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
         </is>
       </c>
       <c r="O207" s="6" t="inlineStr"/>
@@ -19536,12 +19583,14 @@
           <t xml:space="preserve">VM reports </t>
         </is>
       </c>
-      <c r="R207" s="7" t="n"/>
+      <c r="R207" s="7" t="n">
+        <v>4000</v>
+      </c>
       <c r="S207" s="7" t="n"/>
       <c r="T207" s="8" t="inlineStr"/>
       <c r="U207" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bangalore MOM Jul-2026 + approval email</t>
         </is>
       </c>
     </row>
@@ -19876,12 +19925,12 @@
       </c>
       <c r="I211" s="4" t="inlineStr">
         <is>
-          <t>Mismatch — Overpaid</t>
+          <t>Underpaid — No Risk</t>
         </is>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>No Risk</t>
         </is>
       </c>
       <c r="K211" s="5" t="n">
@@ -20080,12 +20129,12 @@
       </c>
       <c r="I213" s="4" t="inlineStr">
         <is>
-          <t>Mismatch — Overpaid</t>
+          <t>Underpaid — No Risk</t>
         </is>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>No Risk</t>
         </is>
       </c>
       <c r="K213" s="5" t="n">
@@ -20284,12 +20333,12 @@
       </c>
       <c r="I215" s="4" t="inlineStr">
         <is>
-          <t>Mismatch — Overpaid</t>
+          <t>Underpaid — No Risk</t>
         </is>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>No Risk</t>
         </is>
       </c>
       <c r="K215" s="5" t="n">
@@ -20374,24 +20423,24 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G216" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Evidence Missing</t>
-        </is>
-      </c>
-      <c r="H216" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I216" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J216" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G216" s="11" t="inlineStr">
+        <is>
+          <t>Formula Based</t>
+        </is>
+      </c>
+      <c r="H216" s="11" t="inlineStr">
+        <is>
+          <t>Formulated</t>
+        </is>
+      </c>
+      <c r="I216" s="11" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J216" s="11" t="inlineStr">
+        <is>
+          <t>No Risk</t>
         </is>
       </c>
       <c r="K216" s="5" t="n">
@@ -20405,12 +20454,12 @@
       </c>
       <c r="N216" s="6" t="inlineStr">
         <is>
-          <t>Driver Acquisition — no calculation structure located
-   - Submitted payout: 1 x ₹625 = ₹625
-Role total = ₹625
-Source entitlement total: not established
-Submitted = ₹625 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>FSE Team Lead (Bangalore) — FSE-TL flat role rate
+   - FSE-TL role rate: 1 x ₹625 = ₹625
+Role total (FSE Incentive Payout Master &gt; Payout_file, row 64) = ₹625
+Source entitlement total: Payout_file final payout ₹625 = ₹625
+Submitted = ₹625 | Variance = ₹0
+Evidence: published FSE-TL rate applied at role level; the same flat rate appears for the other FSE-TL in the file (EF12, Hyderabad), confirming it is a rate-card value, not an ad-hoc amount.</t>
         </is>
       </c>
       <c r="O216" s="6" t="inlineStr"/>
@@ -20425,7 +20474,7 @@
       <c r="T216" s="8" t="inlineStr"/>
       <c r="U216" s="9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FSE Incentive Payout Master &gt; Payout_file</t>
         </is>
       </c>
     </row>
@@ -32680,7 +32729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -32740,7 +32789,7 @@
         <v/>
       </c>
       <c r="D5" s="18">
-        <f>IF($C$20=0,"",C5/$C$20)</f>
+        <f>IF($C$21=0,"",C5/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32759,7 +32808,7 @@
         <v/>
       </c>
       <c r="D6" s="18">
-        <f>IF($C$20=0,"",C6/$C$20)</f>
+        <f>IF($C$21=0,"",C6/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32778,7 +32827,7 @@
         <v/>
       </c>
       <c r="D7" s="18">
-        <f>IF($C$20=0,"",C7/$C$20)</f>
+        <f>IF($C$21=0,"",C7/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32797,14 +32846,14 @@
         <v/>
       </c>
       <c r="D8" s="18">
-        <f>IF($C$20=0,"",C8/$C$20)</f>
+        <f>IF($C$21=0,"",C8/$C$21)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Subjective / Evidence Missing</t>
+          <t>Formula Based</t>
         </is>
       </c>
       <c r="B9" s="16">
@@ -32816,14 +32865,14 @@
         <v/>
       </c>
       <c r="D9" s="18">
-        <f>IF($C$20=0,"",C9/$C$20)</f>
+        <f>IF($C$21=0,"",C9/$C$21)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>Formula Based</t>
+          <t>Part Formula + Approved Flat Component</t>
         </is>
       </c>
       <c r="B10" s="16">
@@ -32835,7 +32884,7 @@
         <v/>
       </c>
       <c r="D10" s="18">
-        <f>IF($C$20=0,"",C10/$C$20)</f>
+        <f>IF($C$21=0,"",C10/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32854,7 +32903,7 @@
         <v/>
       </c>
       <c r="D11" s="18">
-        <f>IF($C$20=0,"",C11/$C$20)</f>
+        <f>IF($C$21=0,"",C11/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32873,7 +32922,7 @@
         <v/>
       </c>
       <c r="D12" s="18">
-        <f>IF($C$20=0,"",C12/$C$20)</f>
+        <f>IF($C$21=0,"",C12/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32892,7 +32941,7 @@
         <v/>
       </c>
       <c r="D13" s="18">
-        <f>IF($C$20=0,"",C13/$C$20)</f>
+        <f>IF($C$21=0,"",C13/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32911,7 +32960,7 @@
         <v/>
       </c>
       <c r="D14" s="18">
-        <f>IF($C$20=0,"",C14/$C$20)</f>
+        <f>IF($C$21=0,"",C14/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32930,7 +32979,7 @@
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>IF($C$20=0,"",C15/$C$20)</f>
+        <f>IF($C$21=0,"",C15/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32949,7 +32998,7 @@
         <v/>
       </c>
       <c r="D16" s="18">
-        <f>IF($C$20=0,"",C16/$C$20)</f>
+        <f>IF($C$21=0,"",C16/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32968,7 +33017,7 @@
         <v/>
       </c>
       <c r="D17" s="18">
-        <f>IF($C$20=0,"",C17/$C$20)</f>
+        <f>IF($C$21=0,"",C17/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -32987,7 +33036,7 @@
         <v/>
       </c>
       <c r="D18" s="18">
-        <f>IF($C$20=0,"",C18/$C$20)</f>
+        <f>IF($C$21=0,"",C18/$C$21)</f>
         <v/>
       </c>
     </row>
@@ -33006,25 +33055,44 @@
         <v/>
       </c>
       <c r="D19" s="18">
-        <f>IF($C$20=0,"",C19/$C$20)</f>
+        <f>IF($C$21=0,"",C19/$C$21)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Formula Based (BI)</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>COUNTIF('Not Formulated'!$G$5:$G$352,$A20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="17">
+        <f>SUMIF('Not Formulated'!$G$5:$G$352,$A20,'Not Formulated'!$K$5:$K$352)</f>
+        <v/>
+      </c>
+      <c r="D20" s="18">
+        <f>IF($C$21=0,"",C20/$C$21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="19">
-        <f>SUM(B5:B19)</f>
+      <c r="B21" s="19">
+        <f>SUM(B5:B20)</f>
         <v/>
       </c>
-      <c r="C20" s="13">
-        <f>SUM(C5:C19)</f>
+      <c r="C21" s="13">
+        <f>SUM(C5:C20)</f>
         <v/>
       </c>
-      <c r="D20" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Not_Formulated_Incentive_Traced.xlsx
+++ b/Not_Formulated_Incentive_Traced.xlsx
@@ -18353,7 +18353,7 @@
 Role total = ₹5,000 = ₹5,000
 Source entitlement total: approval email 'Incentive for Employees Based on Performance', Sathish S -&gt; Vikas S / Mithun Jaiswar, 27-Jul-2026 ₹5,000 = ₹5,000
 Submitted = ₹5,000 | Variance = ₹0
-Evidence: amount corroborated by 1 independent source and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in either source.</t>
+Evidence: amount corroborated by 1 independent source and carries a named incentive rule with a component split, but the underlying qualifying-count x rate for the base leg is not published in that source.</t>
         </is>
       </c>
       <c r="O194" s="6" t="inlineStr"/>

--- a/Not_Formulated_Incentive_Traced.xlsx
+++ b/Not_Formulated_Incentive_Traced.xlsx
@@ -5059,7 +5059,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Fixed (roster amount differs)</t>
+          <t>Fixed (multi-month arrear, unevidenced)</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Mismatch — Overpaid</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K50" s="6" t="n">
@@ -5088,15 +5088,14 @@
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>R&amp;M - CNG / Workshop — R&amp;M fixed incentive scheme: eligibility gate + standard rate
-   - Eligibility: '3 Months Completed' = Yes (scheme gate recorded per employee)
-   - Type recorded in roster = Fixed
-   - Roster incentive amount = ₹1,500
-Role total = ₹1,500
-Source entitlement total: Technician Incentive Calc - Delhi &gt; Sheet14 (official R&amp;M roster) ₹1,500 = ₹1,500
+          <t>R&amp;M - CNG / Workshop — prior-month arrear released with the current month
+   - June leg (claimed in manager note): ₹2,400
+   - July leg (claimed in manager note): ₹2,840
+Claimed total = ₹2,400 + ₹2,840 = ₹5,240
+Documented July entitlement = ₹1,500 per Technician Incentive Calc - Delhi &gt; Sheet14 (Denter Tech, Type Fixed)
+Source entitlement total: July ₹1,500; June leg not present in any supplied file = ₹1,500
 Submitted = ₹5,240 | Variance = ₹3,740
-   &lt;-- ₹3,740 above the roster amount; the difference is not documented in the roster.
-Evidence: fixed-rate scheme by design (no count x rate leg); amount and eligibility gate both recorded in the official R&amp;M roster.</t>
+   &lt;-- TWO GAPS: (1) the July leg claimed (₹2,840) is ₹1,340 above the ₹1,500 the Delhi workbook actually records; (2) the June arrear (₹2,400) has no supporting calculation in any file supplied for this audit.</t>
         </is>
       </c>
       <c r="O50" s="7" t="inlineStr">
@@ -5117,7 +5116,7 @@
       <c r="T50" s="9" t="inlineStr"/>
       <c r="U50" s="10" t="inlineStr">
         <is>
-          <t>Delhi R&amp;M roster (Sheet14)</t>
+          <t>Delhi R&amp;M workbook (July leg only)</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5551,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Fixed (roster amount differs)</t>
+          <t>Fixed (multi-month arrear, unevidenced)</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -5562,12 +5561,12 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Mismatch — Overpaid</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K55" s="6" t="n">
@@ -5581,15 +5580,15 @@
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>R&amp;M - CNG / Telecallers — R&amp;M fixed incentive scheme: eligibility gate + standard rate
-   - Eligibility: '3 Months Completed' = Yes (scheme gate recorded per employee)
-   - Type recorded in roster = Fixed
-   - Roster incentive amount = ₹1,500
-Role total = ₹1,500
-Source entitlement total: Technician Incentive Calc - Delhi &gt; Sheet14 (official R&amp;M roster) ₹1,500 = ₹1,500
+          <t>Customer Support Executive — prior-month arrear released with the current month
+   - June leg (claimed in manager note): ₹5,500
+   - July leg (claimed in manager note): ₹2,500
+Claimed total = ₹5,500 + ₹2,500 = ₹8,000
+Documented July entitlement = ₹1,500 per Technician Incentive Calc - Delhi &gt; 'Other Designations' tab (28 of 30 days present, 0 unapproved, 3 Months Completed = Yes)
+   - Attendance gate on the July leg: 28 of 30 days present, eligibility recorded as met
+Source entitlement total: July ₹1,500; June leg not present in any supplied file = ₹1,500
 Submitted = ₹8,000 | Variance = ₹6,500
-   &lt;-- ₹6,500 above the roster amount; the difference is not documented in the roster.
-Evidence: fixed-rate scheme by design (no count x rate leg); amount and eligibility gate both recorded in the official R&amp;M roster.</t>
+   &lt;-- TWO GAPS: (1) the July leg claimed (₹2,500) is ₹1,000 above the ₹1,500 the Delhi workbook actually records; (2) the June arrear (₹5,500) has no supporting calculation in any file supplied for this audit.</t>
         </is>
       </c>
       <c r="O55" s="7" t="inlineStr">
@@ -5610,7 +5609,7 @@
       <c r="T55" s="9" t="inlineStr"/>
       <c r="U55" s="10" t="inlineStr">
         <is>
-          <t>Delhi R&amp;M roster (Sheet14)</t>
+          <t>Delhi R&amp;M workbook (July leg only)</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5646,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>Fixed (roster amount differs)</t>
+          <t>Fixed (multi-month arrear, unevidenced)</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -5657,12 +5656,12 @@
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Mismatch</t>
+          <t>Mismatch — Overpaid</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K56" s="6" t="n">
@@ -5676,15 +5675,15 @@
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>R&amp;M - CNG / Breakdown — R&amp;M fixed incentive scheme: eligibility gate + standard rate
-   - Eligibility: '3 Months Completed' = Yes (scheme gate recorded per employee)
-   - Type recorded in roster = Fixed
-   - Roster incentive amount = ₹1,500
-Role total = ₹1,500
-Source entitlement total: Technician Incentive Calc - Delhi &gt; Sheet14 (official R&amp;M roster) ₹1,500 = ₹1,500
+          <t>Customer Support Executive — prior-month arrear released with the current month
+   - June leg (claimed in manager note): ₹2,550
+   - July leg (claimed in manager note): ₹1,865
+Claimed total = ₹2,550 + ₹1,865 = ₹4,415
+Documented July entitlement = ₹1,500 per Technician Incentive Calc - Delhi &gt; 'Other Designations' tab (28 of 30 days present, 0 unapproved, 3 Months Completed = Yes)
+   - Attendance gate on the July leg: 28 of 30 days present, eligibility recorded as met
+Source entitlement total: July ₹1,500; June leg not present in any supplied file = ₹1,500
 Submitted = ₹4,415 | Variance = ₹2,915
-   &lt;-- ₹2,915 above the roster amount; the difference is not documented in the roster.
-Evidence: fixed-rate scheme by design (no count x rate leg); amount and eligibility gate both recorded in the official R&amp;M roster.</t>
+   &lt;-- TWO GAPS: (1) the July leg claimed (₹1,865) is ₹365 above the ₹1,500 the Delhi workbook actually records; (2) the June arrear (₹2,550) has no supporting calculation in any file supplied for this audit.</t>
         </is>
       </c>
       <c r="O56" s="7" t="inlineStr">
@@ -5705,7 +5704,7 @@
       <c r="T56" s="9" t="inlineStr"/>
       <c r="U56" s="10" t="inlineStr">
         <is>
-          <t>Delhi R&amp;M roster (Sheet14)</t>
+          <t>Delhi R&amp;M workbook (July leg only)</t>
         </is>
       </c>
     </row>
@@ -11049,43 +11048,44 @@
           <t>Telecalling</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>Subjective / Fixed</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>Not Formulated</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="inlineStr">
-        <is>
-          <t>Insufficient Evidence</t>
-        </is>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Formula Based + Central Component</t>
+        </is>
+      </c>
+      <c r="H113" s="5" t="inlineStr">
+        <is>
+          <t>Formulated</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J113" s="5" t="inlineStr">
+        <is>
+          <t>No Risk</t>
         </is>
       </c>
       <c r="K113" s="6" t="n">
         <v>7600</v>
       </c>
       <c r="L113" s="6" t="n">
-        <v>0</v>
+        <v>7597</v>
       </c>
       <c r="M113" s="6" t="n">
-        <v>-7600</v>
+        <v>-3</v>
       </c>
       <c r="N113" s="7" t="inlineStr">
         <is>
-          <t>Performance Marketing / Telecalling — no calculation structure located
-   - Submitted payout: 1 x ₹7,600 = ₹7,600
-Role total = ₹7,600
-Source entitlement total: not established
-Submitted = ₹7,600 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Performance Marketing / Telecalling — central Recruitment incentive + internal Own Now add-on
+   - Own Now leg: EMI Cab Sold row 43 ('Siraj_021053'), count 1 -&gt; ₹2,000
+   - Central Recruitment leg (22-Jun-2026 to 19-Jul-2026): ₹5,597
+Role total = ₹2,000 + ₹5,597 = ₹7,597
+Source entitlement total: New Incentive Structure_Delhi &gt; EMI Cab Sold!AG43 ₹2,000; Central Recruitment ₹5,597 = ₹7,597
+Submitted = ₹7,600 | Variance = ₹3
+Evidence: the Own Now leg is verified cell-level in the Delhi workbook. The central Recruitment leg is taken from the manager's citation and was not re-derived from the central file, so the 2 legs reconcile to within Rs3 (rounding).</t>
         </is>
       </c>
       <c r="O113" s="7" t="inlineStr">
@@ -11100,11 +11100,17 @@
       </c>
       <c r="Q113" s="7" t="inlineStr"/>
       <c r="R113" s="8" t="n"/>
-      <c r="S113" s="8" t="n"/>
-      <c r="T113" s="9" t="inlineStr"/>
+      <c r="S113" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T113" s="9" t="inlineStr">
+        <is>
+          <t>Own Now (EMI Cab Sold)</t>
+        </is>
+      </c>
       <c r="U113" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EMI Cab Sold!AG43 + Central Recruitment</t>
         </is>
       </c>
     </row>
@@ -14551,22 +14557,22 @@
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>Part Formula + Subjective/Incomplete Evidence</t>
+          <t>Formula Based + Prior-month arrear</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
-          <t>Not Formulated</t>
+          <t>Part Formulated</t>
         </is>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>Insufficient Evidence</t>
+          <t>Mismatch — Overpaid</t>
         </is>
       </c>
       <c r="J152" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K152" s="6" t="n">
@@ -14580,12 +14586,14 @@
       </c>
       <c r="N152" s="7" t="inlineStr">
         <is>
-          <t>Offline growth / Field Sales — no calculation structure located
-   - Submitted payout: 1 x ₹24,500 = ₹24,500
-Role total = ₹24,500
-Source entitlement total: not established
-Submitted = ₹24,500 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Offline growth / Field Sales — FSE payout, current month documented + prior-month arrear
+   - July leg: ₹13,500 per FSE Incentive Payout Master &gt; Payout_file ('EMP ID / Name / Final Amount' block, row 32: lalit_ef12672)
+     (the same employee also carries a D2O conversion line: 14 D2O conversions -&gt; ₹2,200 in the main Payout_file list, row 7)
+   - June leg (claimed in manager note): ₹11,000
+Role total = ₹13,500 + ₹11,000 = ₹24,500
+Source entitlement total: FSE Payout Master July ₹13,500; June leg not in any supplied file = ₹13,500
+Submitted = ₹24,500 | Variance vs documented July = ₹11,000
+   &lt;-- the July leg matches the payout master exactly; the ₹11,000 June arrear has no supporting calculation in any file supplied for this audit.</t>
         </is>
       </c>
       <c r="O152" s="7" t="inlineStr"/>
@@ -14596,11 +14604,17 @@
       </c>
       <c r="Q152" s="7" t="inlineStr"/>
       <c r="R152" s="8" t="n"/>
-      <c r="S152" s="8" t="n"/>
-      <c r="T152" s="9" t="inlineStr"/>
+      <c r="S152" s="8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="T152" s="9" t="inlineStr">
+        <is>
+          <t>June arrear (unevidenced)</t>
+        </is>
+      </c>
       <c r="U152" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FSE Payout Master (July leg)</t>
         </is>
       </c>
     </row>
@@ -14637,7 +14651,7 @@
       </c>
       <c r="G153" s="4" t="inlineStr">
         <is>
-          <t>Part Formula + Subjective/Incomplete Evidence</t>
+          <t>Identity conflict — unresolved</t>
         </is>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -14652,26 +14666,28 @@
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K153" s="6" t="n">
         <v>4620</v>
       </c>
       <c r="L153" s="6" t="n">
-        <v>4620</v>
+        <v>3500</v>
       </c>
       <c r="M153" s="6" t="n">
-        <v>0</v>
+        <v>-1120</v>
       </c>
       <c r="N153" s="7" t="inlineStr">
         <is>
-          <t>Offline growth / Vendor Engagememt — no calculation structure located
-   - Submitted payout: 1 x ₹4,620 = ₹4,620
-Role total = ₹4,620
-Source entitlement total: not established
-Submitted = ₹4,620 | Variance = not computable
-Basis: no employee-level qualifying-count x rate/slab calculation, and no manager annotation, found in the supplied sources.</t>
+          <t>Offline growth / Vendor Engagement — three-way conflict, unresolved
+   - Audit row records: name 'Arpit', amount ₹4,620
+   - FSE Incentive Payout Master &gt; Payout_file row 44 records the SAME ET ID (EF11437) as name 'Ratan', role 'Vendor KAM', Delhi NCR, amount ₹3,500
+   - City manager annotation on this row: 'Not in our incentive list. Remove.'
+Role total (payout master) = ₹3,500
+Source entitlement total: Payout_file ₹3,500 = ₹3,500
+Submitted = ₹4,620 | Variance = ₹1,120
+   &lt;-- DO NOT CLOSE ON THIS ROW: the employee ID maps to a different person in the payout master, the amount differs, and the city manager has asked for the row to be removed entirely. Identity must be resolved before any payment conclusion is drawn.</t>
         </is>
       </c>
       <c r="O153" s="7" t="inlineStr"/>
@@ -14686,7 +14702,7 @@
       <c r="T153" s="9" t="inlineStr"/>
       <c r="U153" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FSE Payout_file row 44 (name mismatch)</t>
         </is>
       </c>
     </row>
@@ -32853,7 +32869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -32913,7 +32929,7 @@
         <v/>
       </c>
       <c r="D5" s="17">
-        <f>IF($C$20=0,"",C5/$C$20)</f>
+        <f>IF($C$24=0,"",C5/$C$24)</f>
         <v/>
       </c>
     </row>
@@ -32932,7 +32948,7 @@
         <v/>
       </c>
       <c r="D6" s="17">
-        <f>IF($C$20=0,"",C6/$C$20)</f>
+        <f>IF($C$24=0,"",C6/$C$24)</f>
         <v/>
       </c>
     </row>
@@ -32951,14 +32967,14 @@
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>IF($C$20=0,"",C7/$C$20)</f>
+        <f>IF($C$24=0,"",C7/$C$24)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Subjective / Fixed</t>
+          <t>Formula Based</t>
         </is>
       </c>
       <c r="B8" s="15">
@@ -32970,14 +32986,14 @@
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>IF($C$20=0,"",C8/$C$20)</f>
+        <f>IF($C$24=0,"",C8/$C$24)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Formula Based</t>
+          <t>Part Formula + Approved Flat Component</t>
         </is>
       </c>
       <c r="B9" s="15">
@@ -32989,14 +33005,14 @@
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>IF($C$20=0,"",C9/$C$20)</f>
+        <f>IF($C$24=0,"",C9/$C$24)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Part Formula + Approved Flat Component</t>
+          <t>Subjective / Fixed</t>
         </is>
       </c>
       <c r="B10" s="15">
@@ -33008,7 +33024,7 @@
         <v/>
       </c>
       <c r="D10" s="17">
-        <f>IF($C$20=0,"",C10/$C$20)</f>
+        <f>IF($C$24=0,"",C10/$C$24)</f>
         <v/>
       </c>
     </row>
@@ -33027,7 +33043,7 @@
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>IF($C$20=0,"",C11/$C$20)</f>
+        <f>IF($C$24=0,"",C11/$C$24)</f>
         <v/>
       </c>
     </row>
@@ -33046,7 +33062,7 @@
         <v/>
       </c>
       <c r="D12" s="17">
-        <f>IF($C$20=0,"",C12/$C$20)</f>
+        <f>IF($C$24=0,"",C12/$C$24)</f>
         <v/>
       </c>
     </row>
@@ -33065,14 +33081,14 @@
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>IF($C$20=0,"",C13/$C$20)</f>
+        <f>IF($C$24=0,"",C13/$C$24)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Fixed (roster amount differs)</t>
+          <t>Fixed (multi-month arrear, unevidenced)</t>
         </is>
       </c>
       <c r="B14" s="15">
@@ -33084,7 +33100,7 @@
         <v/>
       </c>
       <c r="D14" s="17">
-        <f>IF($C$20=0,"",C14/$C$20)</f>
+        <f>IF($C$24=0,"",C14/$C$24)</f>
         <v/>
       </c>
     </row>
@@ -33103,7 +33119,7 @@
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>IF($C$20=0,"",C15/$C$20)</f>
+        <f>IF($C$24=0,"",C15/$C$24)</f>
         <v/>
       </c>
     </row>
@@ -33122,7 +33138,7 @@
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IF($C$20=0,"",C16/$C$20)</f>
+        <f>IF($C$24=0,"",C16/$C$24)</f>
         <v/>
       </c>
     </row>
@@ -33141,14 +33157,14 @@
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IF($C$20=0,"",C17/$C$20)</f>
+        <f>IF($C$24=0,"",C17/$C$24)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Fixed + Special allowance</t>
+          <t>Fixed (roster amount differs)</t>
         </is>
       </c>
       <c r="B18" s="15">
@@ -33160,14 +33176,14 @@
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IF($C$20=0,"",C18/$C$20)</f>
+        <f>IF($C$24=0,"",C18/$C$24)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Formula Based (BI)</t>
+          <t>Fixed + Special allowance</t>
         </is>
       </c>
       <c r="B19" s="15">
@@ -33179,25 +33195,101 @@
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IF($C$20=0,"",C19/$C$20)</f>
+        <f>IF($C$24=0,"",C19/$C$24)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Formula Based + Central Component</t>
+        </is>
+      </c>
+      <c r="B20" s="15">
+        <f>COUNTIF('Not Formulated'!$G$5:$G$352,$A20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="16">
+        <f>SUMIF('Not Formulated'!$G$5:$G$352,$A20,'Not Formulated'!$K$5:$K$352)</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>IF($C$24=0,"",C20/$C$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Formula Based + Prior-month arrear</t>
+        </is>
+      </c>
+      <c r="B21" s="15">
+        <f>COUNTIF('Not Formulated'!$G$5:$G$352,$A21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="16">
+        <f>SUMIF('Not Formulated'!$G$5:$G$352,$A21,'Not Formulated'!$K$5:$K$352)</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>IF($C$24=0,"",C21/$C$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Identity conflict — unresolved</t>
+        </is>
+      </c>
+      <c r="B22" s="15">
+        <f>COUNTIF('Not Formulated'!$G$5:$G$352,$A22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="16">
+        <f>SUMIF('Not Formulated'!$G$5:$G$352,$A22,'Not Formulated'!$K$5:$K$352)</f>
+        <v/>
+      </c>
+      <c r="D22" s="17">
+        <f>IF($C$24=0,"",C22/$C$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Formula Based (BI)</t>
+        </is>
+      </c>
+      <c r="B23" s="15">
+        <f>COUNTIF('Not Formulated'!$G$5:$G$352,$A23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="16">
+        <f>SUMIF('Not Formulated'!$G$5:$G$352,$A23,'Not Formulated'!$K$5:$K$352)</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>IF($C$24=0,"",C23/$C$24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="18">
-        <f>SUM(B5:B19)</f>
+      <c r="B24" s="18">
+        <f>SUM(B5:B23)</f>
         <v/>
       </c>
-      <c r="C20" s="12">
-        <f>SUM(C5:C19)</f>
+      <c r="C24" s="12">
+        <f>SUM(C5:C23)</f>
         <v/>
       </c>
-      <c r="D20" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
